--- a/Luban/Data/#weapon.xlsx
+++ b/Luban/Data/#weapon.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,7 +693,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
         <v>0</v>
       </c>
@@ -745,8 +744,59 @@
       <c r="P4" t="n">
         <v>30</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>霰弹枪</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>shotgun</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>semi</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>75</v>
+      </c>
+      <c r="I5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K5" t="n">
+        <v>168</v>
+      </c>
+      <c r="L5" t="n">
+        <v>30</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>40</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Luban/Data/#weapon.xlsx
+++ b/Luban/Data/#weapon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,16 @@
           <t>sfx</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>max_reserve_ammo</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -599,6 +609,16 @@
           <t>string</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -689,6 +709,16 @@
       <c r="R3" t="inlineStr">
         <is>
           <t>音效（表现后置）</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>备弹上限（0=无限）</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>图标资源名（表现后置）</t>
         </is>
       </c>
     </row>
@@ -744,6 +774,24 @@
       <c r="P4" t="n">
         <v>30</v>
       </c>
+      <c r="S4" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>fx_muzzle_flash</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>sfx_gun_fire_rifle_01</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>ICON_SM_Wep_Preset_B_Rifle_03_Military_Clean</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -796,6 +844,9 @@
       </c>
       <c r="P5" t="n">
         <v>40</v>
+      </c>
+      <c r="S5" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Data/#weapon.xlsx
+++ b/Luban/Data/#weapon.xlsx
@@ -748,7 +748,7 @@
         <v>16</v>
       </c>
       <c r="H4" t="n">
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="I4" t="n">
         <v>30</v>
@@ -774,18 +774,18 @@
       <c r="P4" t="n">
         <v>30</v>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>fx_muzzle_flash</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>sfx_gun_fire_rifle_01</t>
+        </is>
+      </c>
       <c r="S4" t="n">
         <v>90</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>fx_muzzle_flash</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>sfx_gun_fire_rifle_01</t>
-        </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
